--- a/PWA-WEB/shared/assets/plantilla-carga-mensual-5s.xlsx
+++ b/PWA-WEB/shared/assets/plantilla-carga-mensual-5s.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samir\Documents\GitHub\plataforma-operativa-latam400\PWA-WEB\shared\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2023FA31-28C0-448A-ADF4-DEC1E3EB7364}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D010AA08-8557-4D72-AB83-C424F4EC8895}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="9765" xr2:uid="{57C9EC37-9EFE-4292-B551-890A16FD3EB3}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="9765" firstSheet="1" activeTab="1" xr2:uid="{1520EFB3-ED97-4F29-AA22-E88D56BF93C3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Carga 5S" sheetId="1" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="veryHidden" r:id="rId1"/>
+    <sheet name="Carga 5S" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="ListaSupervisores">Listas!$B$1:$B$3</definedName>
+    <definedName name="ListaTurnos">Listas!$A$1:$A$3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
   <si>
     <t>SUPERVISOR</t>
   </si>
@@ -160,6 +165,24 @@
   </si>
   <si>
     <t>Cuarto de Limpieza de Cleaned</t>
+  </si>
+  <si>
+    <t>DIA</t>
+  </si>
+  <si>
+    <t>NOCHE</t>
+  </si>
+  <si>
+    <t>INTERMEDIO</t>
+  </si>
+  <si>
+    <t>MELQUIADES PANGALIMA</t>
+  </si>
+  <si>
+    <t>ALONSO LARICO</t>
+  </si>
+  <si>
+    <t>JONATHAN QUINTANILLA</t>
   </si>
 </sst>
 </file>
@@ -547,7 +570,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83C62CCD-AD51-4E20-B862-EC82043AEA63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD04FF0-6CF4-4BEC-ADD2-A4A21D1BC0E2}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D2AF8FC-32A8-4932-8320-846F36DD0ACA}">
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -979,25 +1037,11 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B34" xr:uid="{91FAFF11-9CA3-496F-9F95-B6FA27D9A151}">
-      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x12ac">
-          <x12ac:list>"DIA,NOCHE,INTERMEDIO"</x12ac:list>
-        </mc:Choice>
-        <mc:Fallback>
-          <formula1>"DIA,NOCHE,INTERMEDIO"</formula1>
-        </mc:Fallback>
-      </mc:AlternateContent>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B34" xr:uid="{AF20AB22-1234-462F-B32D-E06034D06F98}">
+      <formula1>ListaTurnos</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A34" xr:uid="{B8DCFD63-0524-4E52-A832-F4F2C379378F}">
-      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x12ac">
-          <x12ac:list>"MELQUIADES PANGALIMA,ALONSO LARICO,JONATHAN QUINTANILLA"</x12ac:list>
-        </mc:Choice>
-        <mc:Fallback>
-          <formula1>"MELQUIADES PANGALIMA,ALONSO LARICO,JONATHAN QUINTANILLA"</formula1>
-        </mc:Fallback>
-      </mc:AlternateContent>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A34" xr:uid="{96D85C9A-3C20-4CBA-B6F3-DFCE9758E555}">
+      <formula1>ListaSupervisores</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
